--- a/excel-files/QUEZON CITY/SAN BARTOLOME ES.xlsx
+++ b/excel-files/QUEZON CITY/SAN BARTOLOME ES.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29711"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29917"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="146" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0A5DC9E1-3424-4869-9124-B1F3E6CB7470}"/>
+  <xr:revisionPtr revIDLastSave="151" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F7DE5BA7-D4CA-45BF-A86B-05CC45311812}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TextBooks" sheetId="1" r:id="rId1"/>
@@ -5358,8 +5358,8 @@
   </protectedRanges>
   <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E14:E19 E21:E29 E31:E39 E51:E59 E61:E69 E41:E49 E2:E6 E71:E79 E81:E89 E8:E12 E91:E98" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E91:E98 E81:E89 E71:E79 E61:E69 E51:E59 E41:E49 E31:E39 E21:E29 E14:E19 E8:E11 E2:E6 E12" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F21:F29 F31:F39 F41:F49 F51:F59 F61:F69 F71:F79 F81:F89 F2:F6 F8:F12 F91:F98" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
       <formula1>"CO,RO,SDO"</formula1>
@@ -5374,7 +5374,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0858F8C8-8AF8-4852-B88C-61047AF726C8}">
-  <dimension ref="A1:AA157"/>
+  <dimension ref="A1:AA127"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -13477,186 +13477,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:27">
-      <c r="J128" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="129" spans="10:10">
-      <c r="J129" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="130" spans="10:10">
-      <c r="J130" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="131" spans="10:10">
-      <c r="J131" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="132" spans="10:10">
-      <c r="J132" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="133" spans="10:10">
-      <c r="J133" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="134" spans="10:10">
-      <c r="J134" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="135" spans="10:10">
-      <c r="J135" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="136" spans="10:10">
-      <c r="J136" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="137" spans="10:10">
-      <c r="J137" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="138" spans="10:10">
-      <c r="J138" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="139" spans="10:10">
-      <c r="J139" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="140" spans="10:10">
-      <c r="J140" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="141" spans="10:10">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="10:10">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="10:10">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="10:10">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2:C3 C14:C21 C23:C31 C33:C41 C43:C51 C53:C61 C63:C71 C73:C81 C83:C91 C93:C101 C103:C110 C112:C127 C5:C12" name="Textbooks"/>
@@ -13674,11 +13494,11 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S112:S127 M112:M127 Y112:Y127 G112:G127" xr:uid="{8289B4A9-982E-4C7E-A8E2-4BF3404561DB}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X23:X31 X33:X41 X43:X51 X63:X71 X73:X81 X53:X61 L112:L127 X83:X91 X93:X101 X14:X21 X5:X12 L23:L31 L33:L41 L43:L51 L63:L71 L73:L81 L53:L61 R112:R127 L83:L91 L93:L101 L14:L21 L5:L12 R23:R31 R33:R41 R43:R51 R63:R71 R73:R81 R53:R61 F112:F127 R83:R91 R93:R101 R14:R21 R5:R12 F23:F31 F33:F41 F43:F51 F63:F71 F73:F81 F53:F61 F5:F12 F83:F91 F93:F101 F14:F21 F103:F110 R103:R110 L103:L110 X103:X110 X112:X127" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
-      <formula1>"2024,2025"</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M14:M110 Y14:Y110 S4:S110 G5:G12 M5:M12 Y5:Y12 G14:G21 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F112:F127 F103:F110 F93:F101 F83:F91 F73:F81 F63:F71 F53:F61 F43:F51 F33:F41 F23:F31 F14:F21 F5:F12 L112:L127 L103:L110 L93:L101 L83:L91 L73:L81 L63:L71 L53:L61 L43:L51 L33:L41 L23:L31 L14:L21 L5:L12 R112:R127 R103:R110 R93:R101 R83:R91 R73:R81 R63:R71 R53:R61 R43:R51 R33:R41 R23:R31 R14:R21 R5:R12 X112:X127 X103:X110 X93:X101 X83:X91 X73:X81 X63:X71 X53:X61 X43:X51 X33:X41 X23:X31 X14:X21 X4:X12" xr:uid="{063B4DE7-884D-40B8-A273-F600661D0DE8}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13693,7 +13513,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F176E3C0-9A94-45E4-9AFD-70DF8ABE5E5A}">
-  <dimension ref="A1:AB170"/>
+  <dimension ref="A1:AB140"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -22026,186 +21846,6 @@
       <c r="AA140" s="7"/>
       <c r="AB140" s="7"/>
     </row>
-    <row r="141" spans="1:28">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="1:28">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="1:28">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="1:28">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="158" spans="10:10">
-      <c r="J158" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="159" spans="10:10">
-      <c r="J159" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="160" spans="10:10">
-      <c r="J160" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="161" spans="10:10">
-      <c r="J161" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="162" spans="10:10">
-      <c r="J162" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="163" spans="10:10">
-      <c r="J163" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="164" spans="10:10">
-      <c r="J164" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="165" spans="10:10">
-      <c r="J165" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="166" spans="10:10">
-      <c r="J166" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="167" spans="10:10">
-      <c r="J167" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="168" spans="10:10">
-      <c r="J168" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="169" spans="10:10">
-      <c r="J169" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="170" spans="10:10">
-      <c r="J170" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2:C10 C12:C19 C21:C29 C31:C41 C43:C53 C55:C65 C67:C77 C79:C89 C115:C122 C103:C113 C91:C101" name="Textbooks"/>
@@ -22223,8 +21863,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S115:S122 Y115:Y122 G115:G122 Y3:Y10 S3:S10 M3:M10 G3:G10 G12:G19 Y12:Y19 S12:S19 M12:M19 M21:M29 G21:G29 Y21:Y29 S21:S29 S31:S41 M31:M41 G31:G41 Y31:Y41 Y43:Y53 S43:S53 M43:M53 G43:G53 G55:G65 Y55:Y65 S55:S65 M55:M65 M67:M77 G67:G77 Y67:Y77 S67:S77 S79:S89 M79:M89 G79:G89 Y79:Y89 Y91:Y101 S91:S101 M91:M101 G91:G101 G103:G113 Y103:Y113 S103:S113 M103:M113 M115:M122" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X21:X29 X31:X41 X43:X53 X67:X77 X79:X89 X55:X65 X91:X101 X103:X113 X12:X19 X3:X10 L21:L29 L31:L41 L43:L53 L67:L77 L79:L89 L55:L65 L91:L101 L103:L113 L12:L19 L3:L10 R21:R29 R31:R41 R43:R53 R67:R77 R79:R89 R55:R65 R91:R101 R103:R113 R12:R19 R3:R10 F21:F29 F31:F41 F43:F53 F67:F77 F79:F89 F55:F65 F3:F10 F91:F101 X115:X122 F12:F19 F115:F122 R115:R122 L115:L122 F103:F113" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F115:F122 F103:F113 F91:F101 F79:F89 F67:F77 F55:F65 F43:F53 F31:F41 F21:F29 F12:F19 F3:F10 L115:L122 L103:L113 L91:L101 L79:L89 L67:L77 L55:L65 L43:L53 L31:L41 L21:L29 L12:L19 L3:L10 R115:R122 R103:R113 R91:R101 R79:R89 R67:R77 R55:R65 R43:R53 R31:R41 R21:R29 R12:R19 R3:R10 X115:X122 X103:X113 X91:X101 X79:X89 X67:X77 X55:X65 X43:X53 X31:X41 X21:X29 X12:X19 X3:X10" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/excel-files/QUEZON CITY/SAN BARTOLOME ES.xlsx
+++ b/excel-files/QUEZON CITY/SAN BARTOLOME ES.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29917"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10403"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="151" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F7DE5BA7-D4CA-45BF-A86B-05CC45311812}"/>
+  <xr:revisionPtr revIDLastSave="243" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FD6E23CA-B21D-C443-BC1B-F04788FA6434}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TextBooks" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="92">
   <si>
     <t>Grade Level</t>
   </si>
@@ -309,12 +309,18 @@
   <si>
     <t>Arts</t>
   </si>
+  <si>
+    <t>RO</t>
+  </si>
+  <si>
+    <t>CO</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1826,13 +1832,6 @@
       </border>
     </dxf>
     <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -1856,6 +1855,13 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -2934,13 +2940,6 @@
       </border>
     </dxf>
     <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -2977,6 +2976,13 @@
         <top style="thin">
           <color rgb="FF000000"/>
         </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -3019,7 +3025,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DC451CB5-2E69-4EAA-94B0-458F89F93F29}" name="Table2" displayName="Table2" ref="A1:H145" totalsRowShown="0" headerRowDxfId="62" headerRowBorderDxfId="60" tableBorderDxfId="61">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DC451CB5-2E69-4EAA-94B0-458F89F93F29}" name="Table2" displayName="Table2" ref="A1:H145" totalsRowShown="0" headerRowDxfId="62" headerRowBorderDxfId="61" tableBorderDxfId="60">
   <autoFilter ref="A1:H145" xr:uid="{DC451CB5-2E69-4EAA-94B0-458F89F93F29}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{6C961029-0F4E-47F8-B820-C81BD075C863}" name="Grade Level"/>
@@ -3036,7 +3042,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}" name="Table1" displayName="Table1" ref="A2:AA127" totalsRowShown="0" dataDxfId="59" headerRowBorderDxfId="57" tableBorderDxfId="58">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}" name="Table1" displayName="Table1" ref="A2:AA127" totalsRowShown="0" dataDxfId="58" headerRowBorderDxfId="59" tableBorderDxfId="57">
   <autoFilter ref="A2:AA127" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}"/>
   <tableColumns count="27">
     <tableColumn id="1" xr3:uid="{451CCD6B-9C4E-44A3-945A-DE807169F46B}" name="Grade Level" dataDxfId="56"/>
@@ -3092,7 +3098,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9E6A4DE0-FDA1-4B9F-927F-226E420BA323}" name="Table14" displayName="Table14" ref="A2:AA140" totalsRowShown="0" dataDxfId="29" headerRowBorderDxfId="27" tableBorderDxfId="28">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9E6A4DE0-FDA1-4B9F-927F-226E420BA323}" name="Table14" displayName="Table14" ref="A2:AA140" totalsRowShown="0" dataDxfId="28" headerRowBorderDxfId="29" tableBorderDxfId="27">
   <autoFilter ref="A2:AA140" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}"/>
   <tableColumns count="27">
     <tableColumn id="1" xr3:uid="{4B1B9E16-DDB6-464C-9C72-937B3CB9CE66}" name="Grade Level" dataDxfId="26"/>
@@ -3465,17 +3471,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H98"/>
-  <sheetFormatPr defaultRowHeight="13.9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.85546875" customWidth="1"/>
-    <col min="3" max="5" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.140625" customWidth="1"/>
+    <col min="1" max="1" width="10.0859375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.84375" customWidth="1"/>
+    <col min="3" max="5" width="24.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.1015625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.19921875" customWidth="1"/>
     <col min="8" max="8" width="16.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="14" customFormat="1" ht="64.900000000000006" customHeight="1">
+    <row r="1" spans="1:8" s="14" customFormat="1" ht="64.900000000000006" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
@@ -3501,337 +3507,399 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="42.75" customHeight="1">
+    <row r="2" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="5"/>
+      <c r="C2" s="1">
+        <v>325</v>
+      </c>
+      <c r="D2" s="1">
+        <v>473</v>
+      </c>
+      <c r="E2" s="1">
+        <v>2024</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>90</v>
+      </c>
       <c r="G2" s="3">
         <f>IF((C2-D2)&lt;0,0,C2-D2)</f>
         <v>0</v>
       </c>
       <c r="H2" s="4">
         <f>IF((D2-C2)&lt;0,0,D2-C2)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="29.25" customHeight="1">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="5"/>
+      <c r="C3" s="1">
+        <v>325</v>
+      </c>
+      <c r="D3" s="1">
+        <v>473</v>
+      </c>
+      <c r="E3" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>90</v>
+      </c>
       <c r="G3" s="3">
         <f>IF((C3-D3)&lt;0,0,C3-D3)</f>
         <v>0</v>
       </c>
       <c r="H3" s="4">
         <f>IF((D3-C3)&lt;0,0,D3-C3)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="21" customHeight="1">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="5"/>
+      <c r="C4" s="1">
+        <v>325</v>
+      </c>
+      <c r="D4" s="1">
+        <v>473</v>
+      </c>
+      <c r="E4" s="1">
+        <v>2024</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>90</v>
+      </c>
       <c r="G4" s="3">
         <f>IF((C4-D4)&lt;0,0,C4-D4)</f>
         <v>0</v>
       </c>
       <c r="H4" s="4">
         <f>IF((D4-C4)&lt;0,0,D4-C4)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="25.5" customHeight="1">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="5"/>
+      <c r="C5" s="1">
+        <v>325</v>
+      </c>
+      <c r="D5" s="1">
+        <v>473</v>
+      </c>
+      <c r="E5" s="1">
+        <v>2024</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>90</v>
+      </c>
       <c r="G5" s="3">
         <f t="shared" ref="G5:G6" si="0">IF((C5-D5)&lt;0,0,C5-D5)</f>
         <v>0</v>
       </c>
       <c r="H5" s="4">
         <f t="shared" ref="H5:H6" si="1">IF((D5-C5)&lt;0,0,D5-C5)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="19.149999999999999">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>1</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="1"/>
+      <c r="C6" s="1">
+        <v>325</v>
+      </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
       <c r="F6" s="5"/>
       <c r="G6" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>325</v>
       </c>
       <c r="H6" s="4">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="C7" s="6"/>
       <c r="D7" s="6"/>
       <c r="E7" s="6"/>
     </row>
-    <row r="8" spans="1:8" ht="39.75" customHeight="1">
+    <row r="8" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>2</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="1"/>
+      <c r="C8" s="1">
+        <v>355</v>
+      </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
       <c r="F8" s="5"/>
       <c r="G8" s="3">
         <f>IF((C8-D8)&lt;0,0,C8-D8)</f>
-        <v>0</v>
+        <v>355</v>
       </c>
       <c r="H8" s="4">
         <f>IF((D8-C8)&lt;0,0,D8-C8)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="29.25" customHeight="1">
+    <row r="9" spans="1:8" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>2</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="1"/>
+      <c r="C9" s="1">
+        <v>355</v>
+      </c>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
       <c r="F9" s="5"/>
       <c r="G9" s="3">
         <f>IF((C9-D9)&lt;0,0,C9-D9)</f>
-        <v>0</v>
+        <v>355</v>
       </c>
       <c r="H9" s="4">
         <f>IF((D9-C9)&lt;0,0,D9-C9)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="28.5" customHeight="1">
+    <row r="10" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>2</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="1"/>
+      <c r="C10" s="1">
+        <v>355</v>
+      </c>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
       <c r="F10" s="5"/>
       <c r="G10" s="3">
         <f>IF((C10-D10)&lt;0,0,C10-D10)</f>
-        <v>0</v>
+        <v>355</v>
       </c>
       <c r="H10" s="4">
         <f>IF((D10-C10)&lt;0,0,D10-C10)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="24" customHeight="1">
+    <row r="11" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>2</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="5"/>
+      <c r="C11" s="1">
+        <v>355</v>
+      </c>
+      <c r="D11" s="1">
+        <v>500</v>
+      </c>
+      <c r="E11" s="1">
+        <v>2026</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>91</v>
+      </c>
       <c r="G11" s="3">
         <f>IF((C11-D11)&lt;0,0,C11-D11)</f>
         <v>0</v>
       </c>
       <c r="H11" s="4">
         <f>IF((D11-C11)&lt;0,0,D11-C11)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="19.149999999999999">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>2</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="1"/>
+      <c r="C12" s="1">
+        <v>355</v>
+      </c>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
       <c r="F12" s="5"/>
       <c r="G12" s="3">
         <f>IF((C12-D12)&lt;0,0,C12-D12)</f>
-        <v>0</v>
+        <v>355</v>
       </c>
       <c r="H12" s="4">
         <f>IF((D12-C12)&lt;0,0,D12-C12)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
       <c r="E13" s="6"/>
     </row>
-    <row r="14" spans="1:8" ht="49.5" customHeight="1">
+    <row r="14" spans="1:8" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>3</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="1"/>
+      <c r="C14" s="1">
+        <v>405</v>
+      </c>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
       <c r="F14" s="5"/>
       <c r="G14" s="3">
         <f t="shared" ref="G14:G19" si="2">IF((C14-D14)&lt;0,0,C14-D14)</f>
-        <v>0</v>
+        <v>405</v>
       </c>
       <c r="H14" s="4">
         <f t="shared" ref="H14:H19" si="3">IF((D14-C14)&lt;0,0,D14-C14)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="29.25" customHeight="1">
+    <row r="15" spans="1:8" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>3</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C15" s="1"/>
+      <c r="C15" s="1">
+        <v>405</v>
+      </c>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
       <c r="F15" s="5"/>
       <c r="G15" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>405</v>
       </c>
       <c r="H15" s="4">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="27" customHeight="1">
+    <row r="16" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>3</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="1"/>
+      <c r="C16" s="1">
+        <v>405</v>
+      </c>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
       <c r="F16" s="5"/>
       <c r="G16" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>405</v>
       </c>
       <c r="H16" s="4">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="23.25" customHeight="1">
+    <row r="17" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>3</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C17" s="1"/>
+      <c r="C17" s="1">
+        <v>405</v>
+      </c>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
       <c r="F17" s="5"/>
       <c r="G17" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>405</v>
       </c>
       <c r="H17" s="4">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="21" customHeight="1">
+    <row r="18" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>3</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="1"/>
+      <c r="C18" s="1">
+        <v>405</v>
+      </c>
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
       <c r="F18" s="5"/>
       <c r="G18" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>405</v>
       </c>
       <c r="H18" s="4">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="19.149999999999999">
+    <row r="19" spans="1:8" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>3</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C19" s="1"/>
+      <c r="C19" s="1">
+        <v>405</v>
+      </c>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
       <c r="F19" s="5"/>
       <c r="G19" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>405</v>
       </c>
       <c r="H19" s="4">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="7"/>
       <c r="B20" s="7"/>
       <c r="C20" s="8"/>
@@ -3841,187 +3909,247 @@
       <c r="G20" s="7"/>
       <c r="H20" s="7"/>
     </row>
-    <row r="21" spans="1:8" ht="28.5" customHeight="1">
+    <row r="21" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>4</v>
       </c>
       <c r="B21" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C21" s="1"/>
+      <c r="C21" s="1">
+        <v>470</v>
+      </c>
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
       <c r="F21" s="5"/>
       <c r="G21" s="3">
         <f t="shared" ref="G21:G29" si="4">IF((C21-D21)&lt;0,0,C21-D21)</f>
-        <v>0</v>
+        <v>470</v>
       </c>
       <c r="H21" s="4">
         <f t="shared" ref="H21:H29" si="5">IF((D21-C21)&lt;0,0,D21-C21)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="24" customHeight="1">
+    <row r="22" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>4</v>
       </c>
       <c r="B22" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
-      <c r="F22" s="5"/>
+      <c r="C22" s="1">
+        <v>470</v>
+      </c>
+      <c r="D22" s="1">
+        <v>550</v>
+      </c>
+      <c r="E22" s="1">
+        <v>2024</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>91</v>
+      </c>
       <c r="G22" s="3">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H22" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="19.149999999999999">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="18" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>4</v>
       </c>
       <c r="B23" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
-      <c r="F23" s="5"/>
+      <c r="C23" s="1">
+        <v>470</v>
+      </c>
+      <c r="D23" s="1">
+        <v>550</v>
+      </c>
+      <c r="E23" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>91</v>
+      </c>
       <c r="G23" s="3">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H23" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="27" customHeight="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>4</v>
       </c>
       <c r="B24" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="5"/>
+      <c r="C24" s="1">
+        <v>470</v>
+      </c>
+      <c r="D24" s="1">
+        <v>550</v>
+      </c>
+      <c r="E24" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>91</v>
+      </c>
       <c r="G24" s="3">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H24" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="33.75" customHeight="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>4</v>
       </c>
       <c r="B25" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
-      <c r="F25" s="5"/>
+      <c r="C25" s="1">
+        <v>470</v>
+      </c>
+      <c r="D25" s="1">
+        <v>550</v>
+      </c>
+      <c r="E25" s="1">
+        <v>2024</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>91</v>
+      </c>
       <c r="G25" s="3">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H25" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="33.75" customHeight="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>4</v>
       </c>
       <c r="B26" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
-      <c r="F26" s="5"/>
+      <c r="C26" s="1">
+        <v>470</v>
+      </c>
+      <c r="D26" s="1">
+        <v>550</v>
+      </c>
+      <c r="E26" s="1">
+        <v>2024</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>91</v>
+      </c>
       <c r="G26" s="3">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H26" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" ht="33.75" customHeight="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>4</v>
       </c>
       <c r="B27" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
-      <c r="F27" s="5"/>
+      <c r="C27" s="1">
+        <v>470</v>
+      </c>
+      <c r="D27" s="1">
+        <v>550</v>
+      </c>
+      <c r="E27" s="1">
+        <v>2024</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>91</v>
+      </c>
       <c r="G27" s="3">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H27" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" ht="27.75" customHeight="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>4</v>
       </c>
       <c r="B28" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C28" s="1"/>
+      <c r="C28" s="1">
+        <v>470</v>
+      </c>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
       <c r="F28" s="5"/>
       <c r="G28" s="3">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>470</v>
       </c>
       <c r="H28" s="4">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="27.75" customHeight="1">
+    <row r="29" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>4</v>
       </c>
       <c r="B29" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C29" s="1"/>
-      <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
-      <c r="F29" s="5"/>
+      <c r="C29" s="1">
+        <v>470</v>
+      </c>
+      <c r="D29" s="1">
+        <v>550</v>
+      </c>
+      <c r="E29" s="1">
+        <v>2026</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>91</v>
+      </c>
       <c r="G29" s="3">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H29" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" ht="27.75" customHeight="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="7"/>
       <c r="B30" s="7"/>
       <c r="C30" s="8"/>
@@ -4031,7 +4159,7 @@
       <c r="G30" s="7"/>
       <c r="H30" s="7"/>
     </row>
-    <row r="31" spans="1:8" ht="27.75" customHeight="1">
+    <row r="31" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>5</v>
       </c>
@@ -4039,83 +4167,93 @@
         <v>14</v>
       </c>
       <c r="C31" s="1">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="D31" s="1">
         <v>500</v>
       </c>
-      <c r="E31" s="1"/>
-      <c r="F31" s="5"/>
+      <c r="E31" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>91</v>
+      </c>
       <c r="G31" s="3">
         <f t="shared" ref="G31:G39" si="6">IF((C31-D31)&lt;0,0,C31-D31)</f>
         <v>0</v>
       </c>
       <c r="H31" s="4">
         <f t="shared" ref="H31:H39" si="7">IF((D31-C31)&lt;0,0,D31-C31)</f>
-        <v>56</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" ht="27.75" customHeight="1">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>5</v>
       </c>
       <c r="B32" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C32" s="1"/>
+      <c r="C32" s="1">
+        <v>446</v>
+      </c>
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
       <c r="F32" s="5"/>
       <c r="G32" s="3">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>446</v>
       </c>
       <c r="H32" s="4">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="27.75" customHeight="1">
+    <row r="33" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>5</v>
       </c>
       <c r="B33" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C33" s="1"/>
+      <c r="C33" s="1">
+        <v>446</v>
+      </c>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
       <c r="F33" s="5"/>
       <c r="G33" s="3">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>446</v>
       </c>
       <c r="H33" s="4">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="27.75" customHeight="1">
+    <row r="34" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>5</v>
       </c>
       <c r="B34" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C34" s="1"/>
+      <c r="C34" s="1">
+        <v>446</v>
+      </c>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
       <c r="F34" s="5"/>
       <c r="G34" s="3">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>446</v>
       </c>
       <c r="H34" s="4">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="39" customHeight="1">
+    <row r="35" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>5</v>
       </c>
@@ -4123,7 +4261,7 @@
         <v>16</v>
       </c>
       <c r="C35" s="1">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="D35" s="1">
         <v>500</v>
@@ -4131,17 +4269,19 @@
       <c r="E35" s="1">
         <v>2025</v>
       </c>
-      <c r="F35" s="5"/>
+      <c r="F35" s="5" t="s">
+        <v>91</v>
+      </c>
       <c r="G35" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H35" s="4">
         <f t="shared" si="7"/>
-        <v>56</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" ht="27.75" customHeight="1">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>5</v>
       </c>
@@ -4149,23 +4289,27 @@
         <v>13</v>
       </c>
       <c r="C36" s="1">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="D36" s="1">
         <v>500</v>
       </c>
-      <c r="E36" s="1"/>
-      <c r="F36" s="5"/>
+      <c r="E36" s="1">
+        <v>2026</v>
+      </c>
+      <c r="F36" s="5" t="s">
+        <v>91</v>
+      </c>
       <c r="G36" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H36" s="4">
         <f t="shared" si="7"/>
-        <v>56</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" ht="27.75" customHeight="1">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>5</v>
       </c>
@@ -4173,7 +4317,7 @@
         <v>17</v>
       </c>
       <c r="C37" s="1">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="D37" s="1">
         <v>500</v>
@@ -4181,57 +4325,69 @@
       <c r="E37" s="1">
         <v>2025</v>
       </c>
-      <c r="F37" s="5"/>
+      <c r="F37" s="5" t="s">
+        <v>91</v>
+      </c>
       <c r="G37" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H37" s="4">
         <f t="shared" si="7"/>
-        <v>56</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" ht="27.75" customHeight="1">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>5</v>
       </c>
       <c r="B38" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C38" s="1"/>
-      <c r="D38" s="1"/>
-      <c r="E38" s="1"/>
-      <c r="F38" s="5"/>
+      <c r="C38" s="1">
+        <v>446</v>
+      </c>
+      <c r="D38" s="1">
+        <v>500</v>
+      </c>
+      <c r="E38" s="1">
+        <v>2026</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>91</v>
+      </c>
       <c r="G38" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H38" s="4">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" ht="27.75" customHeight="1">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>5</v>
       </c>
       <c r="B39" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C39" s="1"/>
+      <c r="C39" s="1">
+        <v>446</v>
+      </c>
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
       <c r="F39" s="5"/>
       <c r="G39" s="3">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>446</v>
       </c>
       <c r="H39" s="4">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="27.75" customHeight="1">
+    <row r="40" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="7"/>
       <c r="B40" s="7"/>
       <c r="C40" s="8"/>
@@ -4241,187 +4397,205 @@
       <c r="G40" s="7"/>
       <c r="H40" s="7"/>
     </row>
-    <row r="41" spans="1:8" ht="27.75" customHeight="1">
+    <row r="41" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>6</v>
       </c>
       <c r="B41" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C41" s="1"/>
+      <c r="C41" s="1">
+        <v>415</v>
+      </c>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
       <c r="F41" s="5"/>
       <c r="G41" s="3">
         <f t="shared" ref="G41:G49" si="8">IF((C41-D41)&lt;0,0,C41-D41)</f>
-        <v>0</v>
+        <v>415</v>
       </c>
       <c r="H41" s="4">
         <f t="shared" ref="H41:H49" si="9">IF((D41-C41)&lt;0,0,D41-C41)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="27.75" customHeight="1">
+    <row r="42" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>6</v>
       </c>
       <c r="B42" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C42" s="1"/>
+      <c r="C42" s="1">
+        <v>415</v>
+      </c>
       <c r="D42" s="1"/>
       <c r="E42" s="1"/>
       <c r="F42" s="5"/>
       <c r="G42" s="3">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>415</v>
       </c>
       <c r="H42" s="4">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="27.75" customHeight="1">
+    <row r="43" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>6</v>
       </c>
       <c r="B43" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C43" s="1"/>
+      <c r="C43" s="1">
+        <v>415</v>
+      </c>
       <c r="D43" s="1"/>
       <c r="E43" s="1"/>
       <c r="F43" s="5"/>
       <c r="G43" s="3">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>415</v>
       </c>
       <c r="H43" s="4">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="27.75" customHeight="1">
+    <row r="44" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>6</v>
       </c>
       <c r="B44" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C44" s="1"/>
+      <c r="C44" s="1">
+        <v>415</v>
+      </c>
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
       <c r="F44" s="5"/>
       <c r="G44" s="3">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>415</v>
       </c>
       <c r="H44" s="4">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="36.75" customHeight="1">
+    <row r="45" spans="1:8" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>6</v>
       </c>
       <c r="B45" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C45" s="1"/>
+      <c r="C45" s="1">
+        <v>415</v>
+      </c>
       <c r="D45" s="1"/>
       <c r="E45" s="1"/>
       <c r="F45" s="5"/>
       <c r="G45" s="3">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>415</v>
       </c>
       <c r="H45" s="4">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="27.75" customHeight="1">
+    <row r="46" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>6</v>
       </c>
       <c r="B46" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C46" s="1"/>
+      <c r="C46" s="1">
+        <v>415</v>
+      </c>
       <c r="D46" s="1"/>
       <c r="E46" s="1"/>
       <c r="F46" s="5"/>
       <c r="G46" s="3">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>415</v>
       </c>
       <c r="H46" s="4">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="27.75" customHeight="1">
+    <row r="47" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>6</v>
       </c>
       <c r="B47" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C47" s="1"/>
+      <c r="C47" s="1">
+        <v>415</v>
+      </c>
       <c r="D47" s="1"/>
       <c r="E47" s="1"/>
       <c r="F47" s="5"/>
       <c r="G47" s="3">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>415</v>
       </c>
       <c r="H47" s="4">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="27.75" customHeight="1">
+    <row r="48" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>6</v>
       </c>
       <c r="B48" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C48" s="1"/>
+      <c r="C48" s="1">
+        <v>415</v>
+      </c>
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
       <c r="F48" s="5"/>
       <c r="G48" s="3">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>415</v>
       </c>
       <c r="H48" s="4">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="27.75" customHeight="1">
+    <row r="49" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>6</v>
       </c>
       <c r="B49" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C49" s="1"/>
+      <c r="C49" s="1">
+        <v>415</v>
+      </c>
       <c r="D49" s="1"/>
       <c r="E49" s="1"/>
       <c r="F49" s="5"/>
       <c r="G49" s="3">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>415</v>
       </c>
       <c r="H49" s="4">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="27.75" customHeight="1">
+    <row r="50" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="7"/>
       <c r="B50" s="7"/>
       <c r="C50" s="8"/>
@@ -4431,7 +4605,7 @@
       <c r="G50" s="7"/>
       <c r="H50" s="7"/>
     </row>
-    <row r="51" spans="1:8" ht="27.75" customHeight="1">
+    <row r="51" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="10">
         <v>7</v>
       </c>
@@ -4451,7 +4625,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="27.75" customHeight="1">
+    <row r="52" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="10">
         <v>7</v>
       </c>
@@ -4471,7 +4645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="27.75" customHeight="1">
+    <row r="53" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="10">
         <v>7</v>
       </c>
@@ -4491,7 +4665,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="27.75" customHeight="1">
+    <row r="54" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="10">
         <v>7</v>
       </c>
@@ -4511,7 +4685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="39" customHeight="1">
+    <row r="55" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="10">
         <v>7</v>
       </c>
@@ -4531,7 +4705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="27.75" customHeight="1">
+    <row r="56" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="10">
         <v>7</v>
       </c>
@@ -4551,7 +4725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="27.75" customHeight="1">
+    <row r="57" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="10">
         <v>7</v>
       </c>
@@ -4571,7 +4745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="27.75" customHeight="1">
+    <row r="58" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="10">
         <v>7</v>
       </c>
@@ -4591,7 +4765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="27.75" customHeight="1">
+    <row r="59" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="10">
         <v>7</v>
       </c>
@@ -4611,7 +4785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="27.75" customHeight="1">
+    <row r="60" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="7"/>
       <c r="B60" s="7"/>
       <c r="C60" s="8"/>
@@ -4621,7 +4795,7 @@
       <c r="G60" s="7"/>
       <c r="H60" s="7"/>
     </row>
-    <row r="61" spans="1:8" ht="27.75" customHeight="1">
+    <row r="61" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="10">
         <v>8</v>
       </c>
@@ -4641,7 +4815,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="27.75" customHeight="1">
+    <row r="62" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="10">
         <v>8</v>
       </c>
@@ -4661,7 +4835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="27.75" customHeight="1">
+    <row r="63" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="10">
         <v>8</v>
       </c>
@@ -4681,7 +4855,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="27.75" customHeight="1">
+    <row r="64" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="10">
         <v>8</v>
       </c>
@@ -4701,7 +4875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:8" ht="27.75" customHeight="1">
+    <row r="65" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="10">
         <v>8</v>
       </c>
@@ -4721,7 +4895,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="27.75" customHeight="1">
+    <row r="66" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="10">
         <v>8</v>
       </c>
@@ -4741,7 +4915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:8" ht="27.75" customHeight="1">
+    <row r="67" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="10">
         <v>8</v>
       </c>
@@ -4761,7 +4935,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="27.75" customHeight="1">
+    <row r="68" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="10">
         <v>8</v>
       </c>
@@ -4781,7 +4955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:8" ht="27.75" customHeight="1">
+    <row r="69" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="10">
         <v>8</v>
       </c>
@@ -4801,7 +4975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="27.75" customHeight="1">
+    <row r="70" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="7"/>
       <c r="B70" s="7"/>
       <c r="C70" s="8"/>
@@ -4811,7 +4985,7 @@
       <c r="G70" s="7"/>
       <c r="H70" s="7"/>
     </row>
-    <row r="71" spans="1:8" ht="27.75" customHeight="1">
+    <row r="71" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="10">
         <v>9</v>
       </c>
@@ -4831,7 +5005,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="27.75" customHeight="1">
+    <row r="72" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="10">
         <v>9</v>
       </c>
@@ -4851,7 +5025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="27.75" customHeight="1">
+    <row r="73" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="10">
         <v>9</v>
       </c>
@@ -4871,7 +5045,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:8" ht="27.75" customHeight="1">
+    <row r="74" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="10">
         <v>9</v>
       </c>
@@ -4891,7 +5065,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:8" ht="27.75" customHeight="1">
+    <row r="75" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="10">
         <v>9</v>
       </c>
@@ -4911,7 +5085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:8" ht="27.75" customHeight="1">
+    <row r="76" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="10">
         <v>9</v>
       </c>
@@ -4931,7 +5105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:8" ht="27.75" customHeight="1">
+    <row r="77" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="10">
         <v>9</v>
       </c>
@@ -4951,7 +5125,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:8" ht="27.75" customHeight="1">
+    <row r="78" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="10">
         <v>9</v>
       </c>
@@ -4971,7 +5145,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:8" ht="27.75" customHeight="1">
+    <row r="79" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="10">
         <v>9</v>
       </c>
@@ -4991,7 +5165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:8" ht="27.75" customHeight="1">
+    <row r="80" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="7"/>
       <c r="B80" s="8"/>
       <c r="C80" s="8"/>
@@ -5001,7 +5175,7 @@
       <c r="G80" s="7"/>
       <c r="H80" s="7"/>
     </row>
-    <row r="81" spans="1:8" ht="27.75" customHeight="1">
+    <row r="81" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="10">
         <v>10</v>
       </c>
@@ -5021,7 +5195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:8" ht="27.75" customHeight="1">
+    <row r="82" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="10">
         <v>10</v>
       </c>
@@ -5041,7 +5215,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:8" ht="27.75" customHeight="1">
+    <row r="83" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="10">
         <v>10</v>
       </c>
@@ -5061,7 +5235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:8" ht="27.75" customHeight="1">
+    <row r="84" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="10">
         <v>10</v>
       </c>
@@ -5081,7 +5255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:8" ht="27.75" customHeight="1">
+    <row r="85" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="10">
         <v>10</v>
       </c>
@@ -5101,7 +5275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:8" ht="27.75" customHeight="1">
+    <row r="86" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="10">
         <v>10</v>
       </c>
@@ -5121,7 +5295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:8" ht="27.75" customHeight="1">
+    <row r="87" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="10">
         <v>10</v>
       </c>
@@ -5141,7 +5315,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:8" ht="27.75" customHeight="1">
+    <row r="88" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="10">
         <v>10</v>
       </c>
@@ -5161,7 +5335,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:8" ht="27.75" customHeight="1">
+    <row r="89" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="10">
         <v>10</v>
       </c>
@@ -5181,7 +5355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:8" ht="27.75" customHeight="1">
+    <row r="90" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="7"/>
       <c r="B90" s="7"/>
       <c r="C90" s="8"/>
@@ -5191,7 +5365,7 @@
       <c r="G90" s="7"/>
       <c r="H90" s="7"/>
     </row>
-    <row r="91" spans="1:8" ht="39.75" customHeight="1">
+    <row r="91" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>23</v>
       </c>
@@ -5211,7 +5385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:8" ht="27.75" customHeight="1">
+    <row r="92" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>23</v>
       </c>
@@ -5231,7 +5405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:8" ht="27.75" customHeight="1">
+    <row r="93" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>23</v>
       </c>
@@ -5251,7 +5425,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:8" ht="27.75" customHeight="1">
+    <row r="94" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>23</v>
       </c>
@@ -5271,7 +5445,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:8" ht="40.5" customHeight="1">
+    <row r="95" spans="1:8" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>23</v>
       </c>
@@ -5291,7 +5465,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:8" ht="38.25" customHeight="1">
+    <row r="96" spans="1:8" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>23</v>
       </c>
@@ -5311,7 +5485,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:8" ht="27.75" customHeight="1">
+    <row r="97" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>23</v>
       </c>
@@ -5331,7 +5505,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:8" ht="47.25" customHeight="1">
+    <row r="98" spans="1:8" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>23</v>
       </c>
@@ -5358,10 +5532,10 @@
   </protectedRanges>
   <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E91:E98 E81:E89 E71:E79 E61:E69 E51:E59 E41:E49 E31:E39 E21:E29 E14:E19 E8:E11 E2:E6 E12" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E91:E98 E81:E89 E71:E79 E61:E69 E51:E59 E41:E49 E31:E39 E8:E12 E14:E19 E2:E6 E21:E29" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
       <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F21:F29 F31:F39 F41:F49 F51:F59 F61:F69 F71:F79 F81:F89 F2:F6 F8:F12 F91:F98" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F91:F98 F21:F29 F41:F49 F51:F59 F61:F69 F71:F79 F81:F89 F2:F6 F8:F12 F31:F39" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5375,35 +5549,35 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0858F8C8-8AF8-4852-B88C-61047AF726C8}">
   <dimension ref="A1:AA127"/>
-  <sheetFormatPr defaultRowHeight="13.9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.42578125" customWidth="1"/>
-    <col min="2" max="2" width="27.85546875" customWidth="1"/>
-    <col min="3" max="3" width="17.140625" customWidth="1"/>
-    <col min="4" max="4" width="26.140625" customWidth="1"/>
-    <col min="5" max="5" width="23.140625" customWidth="1"/>
-    <col min="6" max="6" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.5703125" customWidth="1"/>
-    <col min="8" max="9" width="20.85546875" customWidth="1"/>
-    <col min="10" max="10" width="13.7109375" customWidth="1"/>
-    <col min="11" max="11" width="35.5703125" customWidth="1"/>
-    <col min="12" max="12" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="31.5703125" customWidth="1"/>
-    <col min="14" max="15" width="20.85546875" customWidth="1"/>
-    <col min="16" max="16" width="21.5703125" customWidth="1"/>
-    <col min="17" max="17" width="33.42578125" customWidth="1"/>
-    <col min="18" max="18" width="25.85546875" customWidth="1"/>
-    <col min="19" max="19" width="32.85546875" customWidth="1"/>
-    <col min="20" max="21" width="20.85546875" customWidth="1"/>
+    <col min="1" max="1" width="9.4140625" customWidth="1"/>
+    <col min="2" max="2" width="27.84375" customWidth="1"/>
+    <col min="3" max="3" width="17.08203125" customWidth="1"/>
+    <col min="4" max="4" width="26.09765625" customWidth="1"/>
+    <col min="5" max="5" width="23.13671875" customWidth="1"/>
+    <col min="6" max="6" width="24.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.5625" customWidth="1"/>
+    <col min="8" max="9" width="20.84765625" customWidth="1"/>
+    <col min="10" max="10" width="13.71875" customWidth="1"/>
+    <col min="11" max="11" width="35.51171875" customWidth="1"/>
+    <col min="12" max="12" width="24.88671875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="31.609375" customWidth="1"/>
+    <col min="14" max="15" width="20.84765625" customWidth="1"/>
+    <col min="16" max="16" width="21.5234375" customWidth="1"/>
+    <col min="17" max="17" width="33.359375" customWidth="1"/>
+    <col min="18" max="18" width="25.828125" customWidth="1"/>
+    <col min="19" max="19" width="32.8203125" customWidth="1"/>
+    <col min="20" max="21" width="20.84765625" customWidth="1"/>
     <col min="22" max="22" width="16.140625" customWidth="1"/>
-    <col min="23" max="23" width="25" customWidth="1"/>
-    <col min="24" max="24" width="15.28515625" customWidth="1"/>
-    <col min="25" max="25" width="20.85546875" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" customWidth="1"/>
-    <col min="27" max="27" width="15.140625" customWidth="1"/>
+    <col min="23" max="23" width="25.01953125" customWidth="1"/>
+    <col min="24" max="24" width="15.33203125" customWidth="1"/>
+    <col min="25" max="25" width="20.84765625" customWidth="1"/>
+    <col min="26" max="26" width="14.796875" customWidth="1"/>
+    <col min="27" max="27" width="15.19921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1">
+    <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D1" s="42" t="s">
         <v>32</v>
       </c>
@@ -5437,7 +5611,7 @@
       <c r="Z1" s="45"/>
       <c r="AA1" s="45"/>
     </row>
-    <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1">
+    <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="15" t="s">
         <v>0</v>
       </c>
@@ -5520,7 +5694,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="30.6" customHeight="1">
+    <row r="3" spans="1:27" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="39" t="s">
         <v>60</v>
       </c>
@@ -5590,7 +5764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="4" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="J4" s="13"/>
       <c r="N4" s="13"/>
       <c r="O4" s="13"/>
@@ -5602,7 +5776,7 @@
       <c r="Z4" s="13"/>
       <c r="AA4" s="13"/>
     </row>
-    <row r="5" spans="1:27" ht="19.149999999999999">
+    <row r="5" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -5671,7 +5845,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="19.149999999999999">
+    <row r="6" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -5740,7 +5914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="19.149999999999999">
+    <row r="7" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>1</v>
       </c>
@@ -5809,7 +5983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="19.149999999999999">
+    <row r="8" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>1</v>
       </c>
@@ -5878,7 +6052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="19.149999999999999">
+    <row r="9" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>1</v>
       </c>
@@ -5947,7 +6121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="19.149999999999999">
+    <row r="10" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>1</v>
       </c>
@@ -6016,7 +6190,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="19.149999999999999">
+    <row r="11" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>1</v>
       </c>
@@ -6085,7 +6259,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="19.149999999999999">
+    <row r="12" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>1</v>
       </c>
@@ -6154,7 +6328,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="13" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="J13" s="13"/>
       <c r="N13" s="13"/>
       <c r="O13" s="13"/>
@@ -6167,7 +6341,7 @@
       <c r="Z13" s="13"/>
       <c r="AA13" s="13"/>
     </row>
-    <row r="14" spans="1:27" ht="19.149999999999999">
+    <row r="14" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>2</v>
       </c>
@@ -6236,7 +6410,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="19.149999999999999">
+    <row r="15" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>2</v>
       </c>
@@ -6305,7 +6479,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="19.5">
+    <row r="16" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>2</v>
       </c>
@@ -6380,7 +6554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="19.5">
+    <row r="17" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>2</v>
       </c>
@@ -6455,7 +6629,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="19.149999999999999">
+    <row r="18" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>2</v>
       </c>
@@ -6524,7 +6698,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="19.5">
+    <row r="19" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>2</v>
       </c>
@@ -6599,7 +6773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="19.5">
+    <row r="20" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>2</v>
       </c>
@@ -6674,7 +6848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="19.149999999999999">
+    <row r="21" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>2</v>
       </c>
@@ -6743,7 +6917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="22" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="J22" s="13"/>
       <c r="M22" s="5"/>
       <c r="N22" s="13"/>
@@ -6757,7 +6931,7 @@
       <c r="Z22" s="13"/>
       <c r="AA22" s="13"/>
     </row>
-    <row r="23" spans="1:27" ht="19.149999999999999">
+    <row r="23" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>3</v>
       </c>
@@ -6826,7 +7000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="19.149999999999999">
+    <row r="24" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>3</v>
       </c>
@@ -6895,7 +7069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="19.5">
+    <row r="25" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>3</v>
       </c>
@@ -6970,7 +7144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="19.5">
+    <row r="26" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>3</v>
       </c>
@@ -7045,7 +7219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="19.5">
+    <row r="27" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>3</v>
       </c>
@@ -7120,7 +7294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="19.5">
+    <row r="28" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>3</v>
       </c>
@@ -7195,7 +7369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="19.5">
+    <row r="29" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>3</v>
       </c>
@@ -7270,7 +7444,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:27" ht="19.5">
+    <row r="30" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>3</v>
       </c>
@@ -7345,7 +7519,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:27" ht="19.149999999999999">
+    <row r="31" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>3</v>
       </c>
@@ -7414,7 +7588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="32" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="J32" s="13"/>
       <c r="M32" s="5"/>
       <c r="N32" s="13"/>
@@ -7428,7 +7602,7 @@
       <c r="Z32" s="13"/>
       <c r="AA32" s="13"/>
     </row>
-    <row r="33" spans="1:27" ht="19.149999999999999">
+    <row r="33" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>4</v>
       </c>
@@ -7497,7 +7671,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="19.149999999999999">
+    <row r="34" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>4</v>
       </c>
@@ -7566,7 +7740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="19.149999999999999">
+    <row r="35" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>4</v>
       </c>
@@ -7635,7 +7809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="19.149999999999999">
+    <row r="36" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>4</v>
       </c>
@@ -7704,7 +7878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="19.149999999999999">
+    <row r="37" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>4</v>
       </c>
@@ -7773,7 +7947,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="19.149999999999999">
+    <row r="38" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>4</v>
       </c>
@@ -7842,7 +8016,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="19.149999999999999">
+    <row r="39" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>4</v>
       </c>
@@ -7911,7 +8085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="19.149999999999999">
+    <row r="40" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>4</v>
       </c>
@@ -7980,7 +8154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="19.5">
+    <row r="41" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>4</v>
       </c>
@@ -8053,7 +8227,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="42" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="J42" s="13"/>
       <c r="M42" s="5"/>
       <c r="N42" s="13"/>
@@ -8067,7 +8241,7 @@
       <c r="Z42" s="13"/>
       <c r="AA42" s="13"/>
     </row>
-    <row r="43" spans="1:27" ht="19.5">
+    <row r="43" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>5</v>
       </c>
@@ -8142,7 +8316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="19.5">
+    <row r="44" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>5</v>
       </c>
@@ -8217,7 +8391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="19.5">
+    <row r="45" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>5</v>
       </c>
@@ -8292,7 +8466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="19.5">
+    <row r="46" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>5</v>
       </c>
@@ -8367,7 +8541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="38.25">
+    <row r="47" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>5</v>
       </c>
@@ -8442,7 +8616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="19.149999999999999">
+    <row r="48" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>5</v>
       </c>
@@ -8511,7 +8685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="19.5">
+    <row r="49" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>5</v>
       </c>
@@ -8586,7 +8760,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="19.5">
+    <row r="50" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>5</v>
       </c>
@@ -8661,7 +8835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="19.5">
+    <row r="51" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>5</v>
       </c>
@@ -8736,7 +8910,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="52" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="J52" s="13"/>
       <c r="M52" s="5"/>
       <c r="N52" s="13"/>
@@ -8750,7 +8924,7 @@
       <c r="Z52" s="13"/>
       <c r="AA52" s="13"/>
     </row>
-    <row r="53" spans="1:27" ht="19.149999999999999">
+    <row r="53" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>6</v>
       </c>
@@ -8819,7 +8993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:27" ht="19.149999999999999">
+    <row r="54" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>6</v>
       </c>
@@ -8888,7 +9062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:27" ht="19.149999999999999">
+    <row r="55" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>6</v>
       </c>
@@ -8957,7 +9131,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:27" ht="19.149999999999999">
+    <row r="56" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>6</v>
       </c>
@@ -9026,7 +9200,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:27" ht="19.149999999999999">
+    <row r="57" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>6</v>
       </c>
@@ -9095,7 +9269,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:27" ht="19.149999999999999">
+    <row r="58" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>6</v>
       </c>
@@ -9164,7 +9338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:27" ht="19.149999999999999">
+    <row r="59" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>6</v>
       </c>
@@ -9233,7 +9407,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:27" ht="19.149999999999999">
+    <row r="60" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>6</v>
       </c>
@@ -9302,7 +9476,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:27" ht="19.149999999999999">
+    <row r="61" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>6</v>
       </c>
@@ -9371,7 +9545,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="62" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="J62" s="13"/>
       <c r="M62" s="5"/>
       <c r="N62" s="13"/>
@@ -9385,7 +9559,7 @@
       <c r="Z62" s="13"/>
       <c r="AA62" s="13"/>
     </row>
-    <row r="63" spans="1:27" ht="19.149999999999999">
+    <row r="63" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A63" s="10">
         <v>7</v>
       </c>
@@ -9454,7 +9628,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:27" ht="19.149999999999999">
+    <row r="64" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A64" s="10">
         <v>7</v>
       </c>
@@ -9523,7 +9697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:27" ht="19.149999999999999">
+    <row r="65" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A65" s="10">
         <v>7</v>
       </c>
@@ -9592,7 +9766,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:27" ht="19.149999999999999">
+    <row r="66" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A66" s="10">
         <v>7</v>
       </c>
@@ -9661,7 +9835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:27" ht="19.149999999999999">
+    <row r="67" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A67" s="10">
         <v>7</v>
       </c>
@@ -9730,7 +9904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:27" ht="19.149999999999999">
+    <row r="68" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A68" s="10">
         <v>7</v>
       </c>
@@ -9799,7 +9973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:27" ht="19.149999999999999">
+    <row r="69" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A69" s="10">
         <v>7</v>
       </c>
@@ -9868,7 +10042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:27" ht="19.149999999999999">
+    <row r="70" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A70" s="10">
         <v>7</v>
       </c>
@@ -9937,7 +10111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:27" ht="19.149999999999999">
+    <row r="71" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A71" s="10">
         <v>7</v>
       </c>
@@ -10006,7 +10180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="72" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="J72" s="13"/>
       <c r="M72" s="5"/>
       <c r="N72" s="13"/>
@@ -10020,7 +10194,7 @@
       <c r="Z72" s="13"/>
       <c r="AA72" s="13"/>
     </row>
-    <row r="73" spans="1:27" ht="19.149999999999999">
+    <row r="73" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A73" s="10">
         <v>8</v>
       </c>
@@ -10089,7 +10263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:27" ht="19.149999999999999">
+    <row r="74" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A74" s="10">
         <v>8</v>
       </c>
@@ -10158,7 +10332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:27" ht="19.149999999999999">
+    <row r="75" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A75" s="10">
         <v>8</v>
       </c>
@@ -10227,7 +10401,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:27" ht="19.149999999999999">
+    <row r="76" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A76" s="10">
         <v>8</v>
       </c>
@@ -10296,7 +10470,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:27" ht="19.149999999999999">
+    <row r="77" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A77" s="10">
         <v>8</v>
       </c>
@@ -10365,7 +10539,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:27" ht="19.149999999999999">
+    <row r="78" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A78" s="10">
         <v>8</v>
       </c>
@@ -10434,7 +10608,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:27" ht="19.149999999999999">
+    <row r="79" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A79" s="10">
         <v>8</v>
       </c>
@@ -10503,7 +10677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:27" ht="19.149999999999999">
+    <row r="80" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A80" s="10">
         <v>8</v>
       </c>
@@ -10572,7 +10746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:27" ht="19.149999999999999">
+    <row r="81" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A81" s="10">
         <v>8</v>
       </c>
@@ -10641,7 +10815,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="82" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="J82" s="13"/>
       <c r="M82" s="5"/>
       <c r="N82" s="13"/>
@@ -10655,7 +10829,7 @@
       <c r="Z82" s="13"/>
       <c r="AA82" s="13"/>
     </row>
-    <row r="83" spans="1:27" ht="19.149999999999999">
+    <row r="83" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A83" s="10">
         <v>9</v>
       </c>
@@ -10724,7 +10898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:27" ht="19.149999999999999">
+    <row r="84" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A84" s="10">
         <v>9</v>
       </c>
@@ -10793,7 +10967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:27" ht="19.149999999999999">
+    <row r="85" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A85" s="10">
         <v>9</v>
       </c>
@@ -10862,7 +11036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:27" ht="19.149999999999999">
+    <row r="86" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A86" s="10">
         <v>9</v>
       </c>
@@ -10931,7 +11105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:27" ht="19.149999999999999">
+    <row r="87" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A87" s="10">
         <v>9</v>
       </c>
@@ -11000,7 +11174,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:27" ht="19.149999999999999">
+    <row r="88" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A88" s="10">
         <v>9</v>
       </c>
@@ -11069,7 +11243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:27" ht="19.149999999999999">
+    <row r="89" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A89" s="10">
         <v>9</v>
       </c>
@@ -11138,7 +11312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:27" ht="19.149999999999999">
+    <row r="90" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A90" s="10">
         <v>9</v>
       </c>
@@ -11207,7 +11381,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:27" ht="19.149999999999999">
+    <row r="91" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A91" s="10">
         <v>9</v>
       </c>
@@ -11276,7 +11450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="92" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="J92" s="13"/>
       <c r="M92" s="5"/>
       <c r="N92" s="13"/>
@@ -11290,7 +11464,7 @@
       <c r="Z92" s="13"/>
       <c r="AA92" s="13"/>
     </row>
-    <row r="93" spans="1:27" ht="19.149999999999999">
+    <row r="93" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A93" s="10">
         <v>10</v>
       </c>
@@ -11359,7 +11533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:27" ht="19.149999999999999">
+    <row r="94" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A94" s="10">
         <v>10</v>
       </c>
@@ -11428,7 +11602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:27" ht="19.149999999999999">
+    <row r="95" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A95" s="10">
         <v>10</v>
       </c>
@@ -11497,7 +11671,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:27" ht="19.149999999999999">
+    <row r="96" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A96" s="10">
         <v>10</v>
       </c>
@@ -11566,7 +11740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:27" ht="19.149999999999999">
+    <row r="97" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A97" s="10">
         <v>10</v>
       </c>
@@ -11635,7 +11809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:27" ht="19.149999999999999">
+    <row r="98" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A98" s="10">
         <v>10</v>
       </c>
@@ -11704,7 +11878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:27" ht="19.149999999999999">
+    <row r="99" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A99" s="10">
         <v>10</v>
       </c>
@@ -11773,7 +11947,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:27" ht="19.149999999999999">
+    <row r="100" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A100" s="10">
         <v>10</v>
       </c>
@@ -11842,7 +12016,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:27" ht="19.149999999999999">
+    <row r="101" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A101" s="10">
         <v>10</v>
       </c>
@@ -11911,7 +12085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="102" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="J102" s="13"/>
       <c r="M102" s="5"/>
       <c r="N102" s="13"/>
@@ -11925,7 +12099,7 @@
       <c r="Z102" s="13"/>
       <c r="AA102" s="13"/>
     </row>
-    <row r="103" spans="1:27" ht="38.450000000000003">
+    <row r="103" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>23</v>
       </c>
@@ -11994,7 +12168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:27" ht="19.149999999999999">
+    <row r="104" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
         <v>23</v>
       </c>
@@ -12063,7 +12237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:27" ht="19.149999999999999">
+    <row r="105" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
         <v>23</v>
       </c>
@@ -12132,7 +12306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:27" ht="19.149999999999999">
+    <row r="106" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
         <v>23</v>
       </c>
@@ -12201,7 +12375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:27" ht="38.450000000000003">
+    <row r="107" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
         <v>23</v>
       </c>
@@ -12270,7 +12444,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:27" ht="19.149999999999999">
+    <row r="108" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>23</v>
       </c>
@@ -12339,7 +12513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:27" ht="38.450000000000003">
+    <row r="109" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
         <v>23</v>
       </c>
@@ -12408,7 +12582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:27" ht="38.450000000000003">
+    <row r="110" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
         <v>23</v>
       </c>
@@ -12477,7 +12651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="111" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="J111" s="13"/>
       <c r="N111" s="13"/>
       <c r="O111" s="13"/>
@@ -12488,7 +12662,7 @@
       <c r="Z111" s="13"/>
       <c r="AA111" s="13"/>
     </row>
-    <row r="112" spans="1:27" ht="19.149999999999999">
+    <row r="112" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A112" s="1"/>
       <c r="B112" s="9"/>
       <c r="C112" s="1"/>
@@ -12550,7 +12724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:27" ht="19.149999999999999">
+    <row r="113" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A113" s="1"/>
       <c r="B113" s="9"/>
       <c r="C113" s="1"/>
@@ -12612,7 +12786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:27" ht="19.149999999999999">
+    <row r="114" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A114" s="1"/>
       <c r="B114" s="9"/>
       <c r="C114" s="1"/>
@@ -12674,7 +12848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:27" ht="19.149999999999999">
+    <row r="115" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A115" s="1"/>
       <c r="B115" s="9"/>
       <c r="C115" s="1"/>
@@ -12736,7 +12910,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:27" ht="19.149999999999999">
+    <row r="116" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A116" s="1"/>
       <c r="B116" s="9"/>
       <c r="C116" s="1"/>
@@ -12798,7 +12972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:27" ht="19.149999999999999">
+    <row r="117" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A117" s="1"/>
       <c r="B117" s="9"/>
       <c r="C117" s="1"/>
@@ -12860,7 +13034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:27" ht="19.149999999999999">
+    <row r="118" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A118" s="1"/>
       <c r="B118" s="9"/>
       <c r="C118" s="1"/>
@@ -12922,7 +13096,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:27" ht="19.149999999999999">
+    <row r="119" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A119" s="1"/>
       <c r="B119" s="9"/>
       <c r="C119" s="1"/>
@@ -12984,7 +13158,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:27" ht="19.149999999999999">
+    <row r="120" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A120" s="1"/>
       <c r="B120" s="9"/>
       <c r="C120" s="1"/>
@@ -13046,7 +13220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:27" ht="19.149999999999999">
+    <row r="121" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A121" s="1"/>
       <c r="B121" s="9"/>
       <c r="C121" s="1"/>
@@ -13108,7 +13282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:27" ht="19.149999999999999">
+    <row r="122" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A122" s="1"/>
       <c r="B122" s="9"/>
       <c r="C122" s="1"/>
@@ -13170,7 +13344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:27" ht="19.149999999999999">
+    <row r="123" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A123" s="1"/>
       <c r="B123" s="9"/>
       <c r="C123" s="1"/>
@@ -13232,7 +13406,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:27" ht="19.149999999999999">
+    <row r="124" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A124" s="1"/>
       <c r="B124" s="9"/>
       <c r="C124" s="1"/>
@@ -13294,7 +13468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:27" ht="19.149999999999999">
+    <row r="125" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A125" s="1"/>
       <c r="B125" s="9"/>
       <c r="C125" s="1"/>
@@ -13356,7 +13530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:27" ht="19.149999999999999">
+    <row r="126" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A126" s="1"/>
       <c r="B126" s="9"/>
       <c r="C126" s="1"/>
@@ -13418,7 +13592,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:27" ht="19.149999999999999">
+    <row r="127" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A127" s="29"/>
       <c r="B127" s="30"/>
       <c r="C127" s="29"/>
@@ -13514,34 +13688,34 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F176E3C0-9A94-45E4-9AFD-70DF8ABE5E5A}">
   <dimension ref="A1:AB140"/>
-  <sheetFormatPr defaultRowHeight="13.9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.42578125" customWidth="1"/>
-    <col min="2" max="2" width="27.85546875" customWidth="1"/>
-    <col min="3" max="3" width="17.140625" customWidth="1"/>
-    <col min="4" max="4" width="16.42578125" customWidth="1"/>
-    <col min="5" max="5" width="23.140625" customWidth="1"/>
-    <col min="6" max="6" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.5703125" customWidth="1"/>
-    <col min="8" max="9" width="20.85546875" customWidth="1"/>
-    <col min="10" max="10" width="13.7109375" customWidth="1"/>
-    <col min="11" max="11" width="24.42578125" customWidth="1"/>
-    <col min="12" max="12" width="18.140625" customWidth="1"/>
-    <col min="13" max="15" width="20.85546875" customWidth="1"/>
-    <col min="16" max="16" width="21.5703125" customWidth="1"/>
-    <col min="17" max="17" width="29.140625" customWidth="1"/>
-    <col min="18" max="18" width="25.85546875" customWidth="1"/>
-    <col min="19" max="19" width="32.85546875" customWidth="1"/>
-    <col min="20" max="21" width="20.85546875" customWidth="1"/>
+    <col min="1" max="1" width="9.4140625" customWidth="1"/>
+    <col min="2" max="2" width="27.84375" customWidth="1"/>
+    <col min="3" max="3" width="17.08203125" customWidth="1"/>
+    <col min="4" max="4" width="16.41015625" customWidth="1"/>
+    <col min="5" max="5" width="23.13671875" customWidth="1"/>
+    <col min="6" max="6" width="24.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.5625" customWidth="1"/>
+    <col min="8" max="9" width="20.84765625" customWidth="1"/>
+    <col min="10" max="10" width="13.71875" customWidth="1"/>
+    <col min="11" max="11" width="24.48046875" customWidth="1"/>
+    <col min="12" max="12" width="18.16015625" customWidth="1"/>
+    <col min="13" max="15" width="20.84765625" customWidth="1"/>
+    <col min="16" max="16" width="21.5234375" customWidth="1"/>
+    <col min="17" max="17" width="29.19140625" customWidth="1"/>
+    <col min="18" max="18" width="25.828125" customWidth="1"/>
+    <col min="19" max="19" width="32.8203125" customWidth="1"/>
+    <col min="20" max="21" width="20.84765625" customWidth="1"/>
     <col min="22" max="22" width="16.140625" customWidth="1"/>
-    <col min="23" max="23" width="25" customWidth="1"/>
-    <col min="24" max="24" width="15.28515625" customWidth="1"/>
-    <col min="25" max="25" width="20.85546875" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" customWidth="1"/>
-    <col min="27" max="27" width="15.140625" customWidth="1"/>
+    <col min="23" max="23" width="25.01953125" customWidth="1"/>
+    <col min="24" max="24" width="15.33203125" customWidth="1"/>
+    <col min="25" max="25" width="20.84765625" customWidth="1"/>
+    <col min="26" max="26" width="14.796875" customWidth="1"/>
+    <col min="27" max="27" width="15.19921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1">
+    <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B1" s="35"/>
       <c r="D1" s="42" t="s">
         <v>32</v>
@@ -13576,7 +13750,7 @@
       <c r="Z1" s="45"/>
       <c r="AA1" s="45"/>
     </row>
-    <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1">
+    <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="15" t="s">
         <v>0</v>
       </c>
@@ -13659,7 +13833,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="19.149999999999999">
+    <row r="3" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -13728,7 +13902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="19.149999999999999">
+    <row r="4" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -13797,7 +13971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="19.149999999999999">
+    <row r="5" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -13866,7 +14040,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="19.149999999999999">
+    <row r="6" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -13935,7 +14109,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="19.149999999999999">
+    <row r="7" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>1</v>
       </c>
@@ -14004,7 +14178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="19.149999999999999">
+    <row r="8" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>1</v>
       </c>
@@ -14073,7 +14247,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="19.149999999999999">
+    <row r="9" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>1</v>
       </c>
@@ -14142,7 +14316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="19.149999999999999">
+    <row r="10" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>1</v>
       </c>
@@ -14211,8 +14385,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:27" s="7" customFormat="1"/>
-    <row r="12" spans="1:27" ht="19.149999999999999">
+    <row r="11" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="12" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>2</v>
       </c>
@@ -14281,7 +14455,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="19.149999999999999">
+    <row r="13" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>2</v>
       </c>
@@ -14350,7 +14524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="19.149999999999999">
+    <row r="14" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>2</v>
       </c>
@@ -14419,7 +14593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="19.5">
+    <row r="15" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>2</v>
       </c>
@@ -14494,7 +14668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="19.5">
+    <row r="16" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>2</v>
       </c>
@@ -14563,7 +14737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="19.5">
+    <row r="17" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>2</v>
       </c>
@@ -14638,7 +14812,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="19.149999999999999">
+    <row r="18" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>2</v>
       </c>
@@ -14707,7 +14881,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="19.149999999999999">
+    <row r="19" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>2</v>
       </c>
@@ -14776,8 +14950,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:27" s="7" customFormat="1"/>
-    <row r="21" spans="1:27" ht="19.149999999999999">
+    <row r="20" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="21" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>3</v>
       </c>
@@ -14846,7 +15020,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="19.149999999999999">
+    <row r="22" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>3</v>
       </c>
@@ -14915,7 +15089,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="19.149999999999999">
+    <row r="23" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>3</v>
       </c>
@@ -14984,7 +15158,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="19.149999999999999">
+    <row r="24" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>3</v>
       </c>
@@ -15053,7 +15227,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="19.149999999999999">
+    <row r="25" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>3</v>
       </c>
@@ -15122,7 +15296,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="19.149999999999999">
+    <row r="26" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>3</v>
       </c>
@@ -15191,7 +15365,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="19.149999999999999">
+    <row r="27" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>3</v>
       </c>
@@ -15260,7 +15434,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="19.149999999999999">
+    <row r="28" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>3</v>
       </c>
@@ -15329,7 +15503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="19.149999999999999">
+    <row r="29" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>3</v>
       </c>
@@ -15398,8 +15572,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:27" s="7" customFormat="1"/>
-    <row r="31" spans="1:27" ht="19.149999999999999">
+    <row r="30" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="31" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>4</v>
       </c>
@@ -15468,7 +15642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:27" ht="19.149999999999999">
+    <row r="32" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>4</v>
       </c>
@@ -15537,7 +15711,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:27" ht="19.149999999999999">
+    <row r="33" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>4</v>
       </c>
@@ -15606,7 +15780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="19.149999999999999">
+    <row r="34" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>4</v>
       </c>
@@ -15675,7 +15849,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="19.149999999999999">
+    <row r="35" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>4</v>
       </c>
@@ -15744,7 +15918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="19.149999999999999">
+    <row r="36" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>4</v>
       </c>
@@ -15813,7 +15987,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="19.149999999999999">
+    <row r="37" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A37" s="37">
         <v>4</v>
       </c>
@@ -15882,7 +16056,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="19.149999999999999">
+    <row r="38" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>4</v>
       </c>
@@ -15951,7 +16125,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="19.149999999999999">
+    <row r="39" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>4</v>
       </c>
@@ -16020,7 +16194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="19.149999999999999">
+    <row r="40" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A40" s="37">
         <v>4</v>
       </c>
@@ -16089,7 +16263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="19.149999999999999">
+    <row r="41" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>4</v>
       </c>
@@ -16158,8 +16332,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:27" s="7" customFormat="1"/>
-    <row r="43" spans="1:27" ht="19.5">
+    <row r="42" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="43" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>5</v>
       </c>
@@ -16234,7 +16408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="19.5">
+    <row r="44" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>5</v>
       </c>
@@ -16303,7 +16477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="19.5">
+    <row r="45" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>5</v>
       </c>
@@ -16378,7 +16552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="19.149999999999999">
+    <row r="46" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>5</v>
       </c>
@@ -16447,7 +16621,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="19.149999999999999">
+    <row r="47" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>5</v>
       </c>
@@ -16516,7 +16690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="19.149999999999999">
+    <row r="48" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>5</v>
       </c>
@@ -16585,7 +16759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="19.149999999999999">
+    <row r="49" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A49" s="37">
         <v>5</v>
       </c>
@@ -16654,7 +16828,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="19.149999999999999">
+    <row r="50" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>5</v>
       </c>
@@ -16723,7 +16897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="19.149999999999999">
+    <row r="51" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>5</v>
       </c>
@@ -16792,7 +16966,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:27" ht="19.149999999999999">
+    <row r="52" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A52" s="37">
         <v>5</v>
       </c>
@@ -16861,7 +17035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:27" ht="19.149999999999999">
+    <row r="53" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>5</v>
       </c>
@@ -16930,8 +17104,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:27" s="7" customFormat="1"/>
-    <row r="55" spans="1:27" ht="19.5">
+    <row r="54" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="55" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>6</v>
       </c>
@@ -17008,7 +17182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:27" ht="19.5">
+    <row r="56" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>6</v>
       </c>
@@ -17083,7 +17257,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:27" ht="19.5">
+    <row r="57" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>6</v>
       </c>
@@ -17158,7 +17332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:27" ht="19.5">
+    <row r="58" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>6</v>
       </c>
@@ -17231,7 +17405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:27" ht="38.25">
+    <row r="59" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>6</v>
       </c>
@@ -17306,7 +17480,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:27" ht="19.5">
+    <row r="60" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>6</v>
       </c>
@@ -17379,7 +17553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:27" ht="19.5">
+    <row r="61" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A61" s="37">
         <v>6</v>
       </c>
@@ -17452,7 +17626,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:27" ht="19.5">
+    <row r="62" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>6</v>
       </c>
@@ -17525,7 +17699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:27" ht="19.149999999999999">
+    <row r="63" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>6</v>
       </c>
@@ -17594,7 +17768,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:27" ht="19.5">
+    <row r="64" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A64" s="37">
         <v>6</v>
       </c>
@@ -17667,7 +17841,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:27" ht="19.5">
+    <row r="65" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>6</v>
       </c>
@@ -17742,8 +17916,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:27" s="7" customFormat="1"/>
-    <row r="67" spans="1:27" ht="19.149999999999999">
+    <row r="66" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="67" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A67" s="10">
         <v>7</v>
       </c>
@@ -17812,7 +17986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:27" ht="19.149999999999999">
+    <row r="68" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A68" s="10">
         <v>7</v>
       </c>
@@ -17881,7 +18055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:27" ht="19.149999999999999">
+    <row r="69" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A69" s="10">
         <v>7</v>
       </c>
@@ -17950,7 +18124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:27" ht="19.149999999999999">
+    <row r="70" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A70" s="10">
         <v>7</v>
       </c>
@@ -18019,7 +18193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:27" ht="19.149999999999999">
+    <row r="71" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A71" s="10">
         <v>7</v>
       </c>
@@ -18088,7 +18262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:27" ht="19.149999999999999">
+    <row r="72" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A72" s="10">
         <v>7</v>
       </c>
@@ -18157,7 +18331,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:27" ht="19.149999999999999">
+    <row r="73" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A73" s="38">
         <v>7</v>
       </c>
@@ -18226,7 +18400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:27" ht="19.149999999999999">
+    <row r="74" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A74" s="10">
         <v>7</v>
       </c>
@@ -18295,7 +18469,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:27" ht="19.149999999999999">
+    <row r="75" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A75" s="10">
         <v>7</v>
       </c>
@@ -18364,7 +18538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:27" ht="19.149999999999999">
+    <row r="76" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A76" s="38">
         <v>7</v>
       </c>
@@ -18433,7 +18607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:27" ht="19.149999999999999">
+    <row r="77" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A77" s="10">
         <v>7</v>
       </c>
@@ -18502,8 +18676,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:27" s="7" customFormat="1"/>
-    <row r="79" spans="1:27" ht="19.149999999999999">
+    <row r="78" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="79" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A79" s="10">
         <v>8</v>
       </c>
@@ -18572,7 +18746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:27" ht="19.149999999999999">
+    <row r="80" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A80" s="10">
         <v>8</v>
       </c>
@@ -18641,7 +18815,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:27" ht="19.149999999999999">
+    <row r="81" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A81" s="10">
         <v>8</v>
       </c>
@@ -18710,7 +18884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:27" ht="19.149999999999999">
+    <row r="82" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A82" s="10">
         <v>8</v>
       </c>
@@ -18779,7 +18953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:27" ht="19.149999999999999">
+    <row r="83" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A83" s="10">
         <v>8</v>
       </c>
@@ -18848,7 +19022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:27" ht="19.149999999999999">
+    <row r="84" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A84" s="10">
         <v>8</v>
       </c>
@@ -18917,7 +19091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:27" ht="19.149999999999999">
+    <row r="85" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A85" s="38">
         <v>8</v>
       </c>
@@ -18986,7 +19160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:27" ht="19.149999999999999">
+    <row r="86" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A86" s="10">
         <v>8</v>
       </c>
@@ -19055,7 +19229,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:27" ht="19.149999999999999">
+    <row r="87" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A87" s="10">
         <v>8</v>
       </c>
@@ -19124,7 +19298,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:27" ht="19.149999999999999">
+    <row r="88" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A88" s="38">
         <v>8</v>
       </c>
@@ -19193,7 +19367,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:27" ht="19.149999999999999">
+    <row r="89" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A89" s="10">
         <v>8</v>
       </c>
@@ -19262,8 +19436,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:27" s="7" customFormat="1"/>
-    <row r="91" spans="1:27" ht="19.149999999999999">
+    <row r="90" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="91" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A91" s="10">
         <v>9</v>
       </c>
@@ -19332,7 +19506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:27" ht="19.149999999999999">
+    <row r="92" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A92" s="10">
         <v>9</v>
       </c>
@@ -19401,7 +19575,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:27" ht="19.149999999999999">
+    <row r="93" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A93" s="10">
         <v>9</v>
       </c>
@@ -19470,7 +19644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:27" ht="19.149999999999999">
+    <row r="94" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A94" s="10">
         <v>9</v>
       </c>
@@ -19539,7 +19713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:27" ht="19.149999999999999">
+    <row r="95" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A95" s="10">
         <v>9</v>
       </c>
@@ -19608,7 +19782,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:27" ht="19.149999999999999">
+    <row r="96" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A96" s="10">
         <v>9</v>
       </c>
@@ -19677,7 +19851,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:27" ht="19.149999999999999">
+    <row r="97" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A97" s="38">
         <v>9</v>
       </c>
@@ -19746,7 +19920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:27" ht="19.149999999999999">
+    <row r="98" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A98" s="10">
         <v>9</v>
       </c>
@@ -19815,7 +19989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:27" ht="19.149999999999999">
+    <row r="99" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A99" s="10">
         <v>9</v>
       </c>
@@ -19884,7 +20058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:27" ht="19.149999999999999">
+    <row r="100" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A100" s="38">
         <v>9</v>
       </c>
@@ -19953,7 +20127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:27" ht="19.149999999999999">
+    <row r="101" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A101" s="10">
         <v>9</v>
       </c>
@@ -20022,8 +20196,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:27" s="7" customFormat="1"/>
-    <row r="103" spans="1:27" ht="19.149999999999999">
+    <row r="102" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="103" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A103" s="10">
         <v>10</v>
       </c>
@@ -20092,7 +20266,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:27" ht="19.149999999999999">
+    <row r="104" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A104" s="10">
         <v>10</v>
       </c>
@@ -20161,7 +20335,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:27" ht="19.149999999999999">
+    <row r="105" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A105" s="10">
         <v>10</v>
       </c>
@@ -20230,7 +20404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:27" ht="19.149999999999999">
+    <row r="106" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A106" s="10">
         <v>10</v>
       </c>
@@ -20299,7 +20473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:27" ht="19.149999999999999">
+    <row r="107" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A107" s="10">
         <v>10</v>
       </c>
@@ -20368,7 +20542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:27" ht="19.149999999999999">
+    <row r="108" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A108" s="10">
         <v>10</v>
       </c>
@@ -20437,7 +20611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:27" ht="19.149999999999999">
+    <row r="109" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A109" s="38">
         <v>10</v>
       </c>
@@ -20506,7 +20680,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:27" ht="19.149999999999999">
+    <row r="110" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A110" s="10">
         <v>10</v>
       </c>
@@ -20575,7 +20749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:27" ht="19.149999999999999">
+    <row r="111" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A111" s="10">
         <v>10</v>
       </c>
@@ -20644,7 +20818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:27" ht="19.149999999999999">
+    <row r="112" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A112" s="38">
         <v>10</v>
       </c>
@@ -20713,7 +20887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:28" ht="19.149999999999999">
+    <row r="113" spans="1:28" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A113" s="10">
         <v>10</v>
       </c>
@@ -20782,8 +20956,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:28" s="7" customFormat="1"/>
-    <row r="115" spans="1:28" ht="38.450000000000003">
+    <row r="114" spans="1:28" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="115" spans="1:28" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
         <v>23</v>
       </c>
@@ -20852,7 +21026,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:28" ht="19.149999999999999">
+    <row r="116" spans="1:28" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
         <v>23</v>
       </c>
@@ -20921,7 +21095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:28" ht="19.149999999999999">
+    <row r="117" spans="1:28" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
         <v>23</v>
       </c>
@@ -20990,7 +21164,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:28" ht="19.149999999999999">
+    <row r="118" spans="1:28" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
         <v>23</v>
       </c>
@@ -21059,7 +21233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:28" ht="38.450000000000003">
+    <row r="119" spans="1:28" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
         <v>23</v>
       </c>
@@ -21128,7 +21302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:28" ht="19.149999999999999">
+    <row r="120" spans="1:28" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
         <v>23</v>
       </c>
@@ -21197,7 +21371,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:28" ht="38.450000000000003">
+    <row r="121" spans="1:28" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
         <v>23</v>
       </c>
@@ -21266,7 +21440,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:28" ht="38.450000000000003">
+    <row r="122" spans="1:28" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
         <v>23</v>
       </c>
@@ -21335,8 +21509,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:28" s="7" customFormat="1"/>
-    <row r="124" spans="1:28">
+    <row r="123" spans="1:28" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="124" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A124" s="7"/>
       <c r="B124" s="7"/>
       <c r="C124" s="7"/>
@@ -21366,7 +21540,7 @@
       <c r="AA124" s="7"/>
       <c r="AB124" s="7"/>
     </row>
-    <row r="125" spans="1:28">
+    <row r="125" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A125" s="7"/>
       <c r="B125" s="7"/>
       <c r="C125" s="7"/>
@@ -21396,7 +21570,7 @@
       <c r="AA125" s="7"/>
       <c r="AB125" s="7"/>
     </row>
-    <row r="126" spans="1:28">
+    <row r="126" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A126" s="7"/>
       <c r="B126" s="7"/>
       <c r="C126" s="7"/>
@@ -21426,7 +21600,7 @@
       <c r="AA126" s="7"/>
       <c r="AB126" s="7"/>
     </row>
-    <row r="127" spans="1:28">
+    <row r="127" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A127" s="7"/>
       <c r="B127" s="7"/>
       <c r="C127" s="7"/>
@@ -21456,7 +21630,7 @@
       <c r="AA127" s="7"/>
       <c r="AB127" s="7"/>
     </row>
-    <row r="128" spans="1:28">
+    <row r="128" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A128" s="7"/>
       <c r="B128" s="7"/>
       <c r="C128" s="7"/>
@@ -21486,7 +21660,7 @@
       <c r="AA128" s="7"/>
       <c r="AB128" s="7"/>
     </row>
-    <row r="129" spans="1:28">
+    <row r="129" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A129" s="7"/>
       <c r="B129" s="7"/>
       <c r="C129" s="7"/>
@@ -21516,7 +21690,7 @@
       <c r="AA129" s="7"/>
       <c r="AB129" s="7"/>
     </row>
-    <row r="130" spans="1:28">
+    <row r="130" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A130" s="7"/>
       <c r="B130" s="7"/>
       <c r="C130" s="7"/>
@@ -21546,7 +21720,7 @@
       <c r="AA130" s="7"/>
       <c r="AB130" s="7"/>
     </row>
-    <row r="131" spans="1:28">
+    <row r="131" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A131" s="7"/>
       <c r="B131" s="7"/>
       <c r="C131" s="7"/>
@@ -21576,7 +21750,7 @@
       <c r="AA131" s="7"/>
       <c r="AB131" s="7"/>
     </row>
-    <row r="132" spans="1:28">
+    <row r="132" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A132" s="7"/>
       <c r="B132" s="7"/>
       <c r="C132" s="7"/>
@@ -21606,7 +21780,7 @@
       <c r="AA132" s="7"/>
       <c r="AB132" s="7"/>
     </row>
-    <row r="133" spans="1:28">
+    <row r="133" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A133" s="7"/>
       <c r="B133" s="7"/>
       <c r="C133" s="7"/>
@@ -21636,7 +21810,7 @@
       <c r="AA133" s="7"/>
       <c r="AB133" s="7"/>
     </row>
-    <row r="134" spans="1:28">
+    <row r="134" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A134" s="7"/>
       <c r="B134" s="7"/>
       <c r="C134" s="7"/>
@@ -21666,7 +21840,7 @@
       <c r="AA134" s="7"/>
       <c r="AB134" s="7"/>
     </row>
-    <row r="135" spans="1:28">
+    <row r="135" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A135" s="7"/>
       <c r="B135" s="7"/>
       <c r="C135" s="7"/>
@@ -21696,7 +21870,7 @@
       <c r="AA135" s="7"/>
       <c r="AB135" s="7"/>
     </row>
-    <row r="136" spans="1:28">
+    <row r="136" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A136" s="7"/>
       <c r="B136" s="7"/>
       <c r="C136" s="7"/>
@@ -21726,7 +21900,7 @@
       <c r="AA136" s="7"/>
       <c r="AB136" s="7"/>
     </row>
-    <row r="137" spans="1:28">
+    <row r="137" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A137" s="7"/>
       <c r="B137" s="7"/>
       <c r="C137" s="7"/>
@@ -21756,7 +21930,7 @@
       <c r="AA137" s="7"/>
       <c r="AB137" s="7"/>
     </row>
-    <row r="138" spans="1:28">
+    <row r="138" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A138" s="7"/>
       <c r="B138" s="7"/>
       <c r="C138" s="7"/>
@@ -21786,7 +21960,7 @@
       <c r="AA138" s="7"/>
       <c r="AB138" s="7"/>
     </row>
-    <row r="139" spans="1:28">
+    <row r="139" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A139" s="7"/>
       <c r="B139" s="7"/>
       <c r="C139" s="7"/>
@@ -21816,7 +21990,7 @@
       <c r="AA139" s="7"/>
       <c r="AB139" s="7"/>
     </row>
-    <row r="140" spans="1:28">
+    <row r="140" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A140" s="7"/>
       <c r="B140" s="7"/>
       <c r="C140" s="7"/>
